--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -14451,11 +14451,11 @@
         </is>
       </c>
       <c r="M132" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Coffee, Spearmint</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -14467,10 +14467,10 @@
         <v>46083.40835648148</v>
       </c>
       <c r="Q132" s="1" t="n">
-        <v>46263.4896875</v>
+        <v>46278.28266203704</v>
       </c>
       <c r="R132" t="n">
-        <v>36</v>
+        <v>40.9</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -50425,11 +50425,11 @@
         </is>
       </c>
       <c r="M470" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N470" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee, Green Burner, Turmeric Curcumin</t>
         </is>
       </c>
       <c r="O470" t="inlineStr">
@@ -50441,10 +50441,10 @@
         <v>46190.55417824074</v>
       </c>
       <c r="Q470" s="1" t="n">
-        <v>46192.55048611111</v>
+        <v>46276.86599537037</v>
       </c>
       <c r="R470" t="n">
-        <v>20.1</v>
+        <v>26</v>
       </c>
       <c r="S470" t="inlineStr">
         <is>

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -49881,8 +49881,16 @@
           <t>https://www.tiktok.com/@hadi.haniya1</t>
         </is>
       </c>
-      <c r="C467" t="inlineStr"/>
-      <c r="D467" t="inlineStr"/>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>1040.12</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr"/>
       <c r="F467" t="inlineStr"/>
       <c r="G467" t="inlineStr"/>

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23434.0</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9080.0</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Health, Food &amp; Beverages, Home Supplies</t>
+          <t>Health, Food &amp; Beverages, Womenswear &amp; Underwear</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>96.23</t>
+          <t>96.62</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.66</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3027.0</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2951.0</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4197,17 +4197,17 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Fashion Accessories, Beauty &amp; Personal Care, Sports &amp; Outdoor</t>
+          <t>Health, Fashion Accessories, Kitchenware</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>95.59</t>
+          <t>95.62</t>
         </is>
       </c>
       <c r="M36" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1064</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -15880,12 +15880,12 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2591.0</t>
+          <t>732</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2429.0</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -15915,17 +15915,17 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Household Appliances, Food &amp; Beverages, Beauty &amp; Personal Care</t>
+          <t>Health, Food &amp; Beverages, Phones &amp; Electronics</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>87.79</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="M146" t="n">
@@ -35570,12 +35570,12 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£5K-£10K</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>10234.0</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -35585,7 +35585,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>4003.0</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -35605,17 +35605,17 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care, Womenswear &amp; Underwear, Household Appliances</t>
+          <t>Beauty &amp; Personal Care, Womenswear &amp; Underwear, Health</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>89.62</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="M332" t="n">
@@ -36185,7 +36185,7 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2606.0</t>
+          <t>2602</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
@@ -36195,7 +36195,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>14163.0</t>
+          <t>13997</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -36215,17 +36215,17 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care, Health, Textiles &amp; Soft Furnishings</t>
+          <t>Beauty &amp; Personal Care, Textiles &amp; Soft Furnishings, Health</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>98.77</t>
+          <t>98.89</t>
         </is>
       </c>
       <c r="M338" t="n">
@@ -43508,7 +43508,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2020.0</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -43518,7 +43518,7 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>2192.0</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
@@ -43538,17 +43538,17 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>Books, Magazines &amp; Audio, Beauty &amp; Personal Care, Furniture</t>
+          <t>Beauty &amp; Personal Care, Books, Magazines &amp; Audio, Household Appliances</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>96.99</t>
+          <t>97.09</t>
         </is>
       </c>
       <c r="M407" t="n">
@@ -44783,12 +44783,12 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£25K-£50K</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>27425</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -44798,12 +44798,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -44814,17 +44814,17 @@
       <c r="I419" t="inlineStr"/>
       <c r="J419" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>Household Appliances, Beauty &amp; Personal Care, Health</t>
+          <t>Household Appliances, Health, Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>77.77</t>
+          <t>90</t>
         </is>
       </c>
       <c r="M419" t="n">
@@ -57075,12 +57075,12 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>837.0</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -57090,7 +57090,7 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>109375.0</t>
+          <t>138824</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
@@ -57110,17 +57110,17 @@
       </c>
       <c r="J535" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="K535" t="inlineStr">
         <is>
-          <t>Health, Food &amp; Beverages, Beauty &amp; Personal Care</t>
+          <t>Beauty &amp; Personal Care, Health, Food &amp; Beverages</t>
         </is>
       </c>
       <c r="L535" t="inlineStr">
         <is>
-          <t>97.22</t>
+          <t>72.57</t>
         </is>
       </c>
       <c r="M535" t="n">
@@ -62311,7 +62311,7 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>16708</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
@@ -62321,7 +62321,7 @@
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>7863</t>
+          <t>7768</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
@@ -62341,17 +62341,17 @@
       </c>
       <c r="J584" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="K584" t="inlineStr">
         <is>
-          <t>Furniture, Textiles &amp; Soft Furnishings, Home Supplies</t>
+          <t>Textiles &amp; Soft Furnishings, Kitchenware, Household Appliances</t>
         </is>
       </c>
       <c r="L584" t="inlineStr">
         <is>
-          <t>67.22</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="M584" t="n">
@@ -74445,16 +74445,52 @@
           <t>https://www.tiktok.com/@im.leez</t>
         </is>
       </c>
-      <c r="C699" t="inlineStr"/>
-      <c r="D699" t="inlineStr"/>
-      <c r="E699" t="inlineStr"/>
-      <c r="F699" t="inlineStr"/>
-      <c r="G699" t="inlineStr"/>
-      <c r="H699" t="inlineStr"/>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>£1K-£5K</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>2265</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>25-34</t>
+        </is>
+      </c>
       <c r="I699" t="inlineStr"/>
-      <c r="J699" t="inlineStr"/>
-      <c r="K699" t="inlineStr"/>
-      <c r="L699" t="inlineStr"/>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Fashion Accessories, Beauty &amp; Personal Care, Household Appliances</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr">
+        <is>
+          <t>63.63</t>
+        </is>
+      </c>
       <c r="M699" t="n">
         <v>1</v>
       </c>
@@ -77391,12 +77427,12 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>£200-£500</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
         <is>
-          <t>493.0</t>
+          <t>2483</t>
         </is>
       </c>
       <c r="E727" t="inlineStr">
@@ -77406,7 +77442,7 @@
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>1417.0</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -77426,17 +77462,17 @@
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>Household Appliances, Health, Automotive &amp; Motorcycle</t>
+          <t>Beauty &amp; Personal Care, Health, Shoes</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="M727" t="n">
@@ -84211,17 +84247,45 @@
       </c>
       <c r="D792" t="inlineStr">
         <is>
-          <t>31518.50</t>
-        </is>
-      </c>
-      <c r="E792" t="inlineStr"/>
-      <c r="F792" t="inlineStr"/>
-      <c r="G792" t="inlineStr"/>
-      <c r="H792" t="inlineStr"/>
+          <t>31485</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>25K-50K</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>35261</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>25-34</t>
+        </is>
+      </c>
       <c r="I792" t="inlineStr"/>
-      <c r="J792" t="inlineStr"/>
-      <c r="K792" t="inlineStr"/>
-      <c r="L792" t="inlineStr"/>
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Kitchenware, Beauty &amp; Personal Care, Household Appliances</t>
+        </is>
+      </c>
+      <c r="L792" t="inlineStr">
+        <is>
+          <t>96.66</t>
+        </is>
+      </c>
       <c r="M792" t="n">
         <v>3</v>
       </c>

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -15101,16 +15101,52 @@
           <t>https://www.tiktok.com/@robsreductions</t>
         </is>
       </c>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>£10K-£25K</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>21718</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>3397</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>35-44</t>
+        </is>
+      </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Home Supplies, Health, Food &amp; Beverages</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>88.17</t>
+        </is>
+      </c>
       <c r="M139" t="n">
         <v>1</v>
       </c>
@@ -28974,16 +29010,52 @@
           <t>https://www.tiktok.com/@thegrandreview</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr"/>
-      <c r="D270" t="inlineStr"/>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>£10K-£25K</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>12760</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>10016</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>35-44</t>
+        </is>
+      </c>
       <c r="I270" t="inlineStr"/>
-      <c r="J270" t="inlineStr"/>
-      <c r="K270" t="inlineStr"/>
-      <c r="L270" t="inlineStr"/>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Household Appliances, Health, Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>98.43</t>
+        </is>
+      </c>
       <c r="M270" t="n">
         <v>3</v>
       </c>
@@ -44574,16 +44646,56 @@
           <t>https://www.tiktok.com/@pia.tts</t>
         </is>
       </c>
-      <c r="C418" t="inlineStr"/>
-      <c r="D418" t="inlineStr"/>
-      <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
-      <c r="G418" t="inlineStr"/>
-      <c r="H418" t="inlineStr"/>
-      <c r="I418" t="inlineStr"/>
-      <c r="J418" t="inlineStr"/>
-      <c r="K418" t="inlineStr"/>
-      <c r="L418" t="inlineStr"/>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>£25K-£50K</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>25148.0</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>1377.0</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care, Household Appliances, Home Supplies</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>94.83</t>
+        </is>
+      </c>
       <c r="M418" t="n">
         <v>2</v>
       </c>
@@ -56822,16 +56934,52 @@
           <t>https://www.tiktok.com/@shopsmartly309</t>
         </is>
       </c>
-      <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr"/>
-      <c r="E534" t="inlineStr"/>
-      <c r="F534" t="inlineStr"/>
-      <c r="G534" t="inlineStr"/>
-      <c r="H534" t="inlineStr"/>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>383.0</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>1K-5K</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>1836.0</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>25-34</t>
+        </is>
+      </c>
       <c r="I534" t="inlineStr"/>
-      <c r="J534" t="inlineStr"/>
-      <c r="K534" t="inlineStr"/>
-      <c r="L534" t="inlineStr"/>
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Womenswear &amp; Underwear, Home Supplies, Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="M534" t="n">
         <v>1</v>
       </c>
@@ -78358,16 +78506,56 @@
           <t>https://www.tiktok.com/@folamegadealshop</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr"/>
-      <c r="D738" t="inlineStr"/>
-      <c r="E738" t="inlineStr"/>
-      <c r="F738" t="inlineStr"/>
-      <c r="G738" t="inlineStr"/>
-      <c r="H738" t="inlineStr"/>
-      <c r="I738" t="inlineStr"/>
-      <c r="J738" t="inlineStr"/>
-      <c r="K738" t="inlineStr"/>
-      <c r="L738" t="inlineStr"/>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>£200-£500</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>248.0</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>10K-25K</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>15008.0</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>Black/African</t>
+        </is>
+      </c>
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Beauty &amp; Personal Care, Home Supplies, Health</t>
+        </is>
+      </c>
+      <c r="L738" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="M738" t="n">
         <v>1</v>
       </c>
@@ -83080,16 +83268,56 @@
           <t>https://www.tiktok.com/@desinukk</t>
         </is>
       </c>
-      <c r="C784" t="inlineStr"/>
-      <c r="D784" t="inlineStr"/>
-      <c r="E784" t="inlineStr"/>
-      <c r="F784" t="inlineStr"/>
-      <c r="G784" t="inlineStr"/>
-      <c r="H784" t="inlineStr"/>
-      <c r="I784" t="inlineStr"/>
-      <c r="J784" t="inlineStr"/>
-      <c r="K784" t="inlineStr"/>
-      <c r="L784" t="inlineStr"/>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>£500-£1K</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>565.0</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>0-1K</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>620.0</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>25-34</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>Mixed/Ambiguous</t>
+        </is>
+      </c>
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>0.59</t>
+        </is>
+      </c>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Health, Shoes, Beauty &amp; Personal Care</t>
+        </is>
+      </c>
+      <c r="L784" t="inlineStr">
+        <is>
+          <t>66.66</t>
+        </is>
+      </c>
       <c r="M784" t="n">
         <v>1</v>
       </c>

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>45910.63778935185</v>
       </c>
       <c r="Q12" s="1" t="n">
-        <v>46306.48752314815</v>
+        <v>46308.37924768519</v>
       </c>
       <c r="R12" t="n">
         <v>47.2</v>
@@ -10409,11 +10409,11 @@
         </is>
       </c>
       <c r="M94" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Hibiscus, Other</t>
+          <t>Ashwagandha Coffee, Green Burner, Hibiscus, Other, Spearmint</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -10425,10 +10425,10 @@
         <v>45915.34108796297</v>
       </c>
       <c r="Q94" s="1" t="n">
-        <v>46307.36116898148</v>
+        <v>46308.29585648148</v>
       </c>
       <c r="R94" t="n">
-        <v>34.5</v>
+        <v>39.4</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -26363,7 +26363,7 @@
         </is>
       </c>
       <c r="M244" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N244" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45841.36015046296</v>
       </c>
       <c r="Q244" s="1" t="n">
-        <v>46304.45837962963</v>
+        <v>46308.37925925926</v>
       </c>
       <c r="R244" t="n">
         <v>71.3</v>
@@ -61115,11 +61115,11 @@
         </is>
       </c>
       <c r="M572" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N572" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee</t>
+          <t>Ashwagandha Coffee, Other</t>
         </is>
       </c>
       <c r="O572" t="inlineStr">
@@ -61131,7 +61131,7 @@
         <v>46232.30774305556</v>
       </c>
       <c r="Q572" s="1" t="n">
-        <v>46232.30774305556</v>
+        <v>46308.37918981481</v>
       </c>
       <c r="R572" t="n">
         <v>6</v>

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -63476,7 +63476,7 @@
         <v>4664</v>
       </c>
       <c r="M635">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N635" t="s">
         <v>4799</v>
@@ -63488,10 +63488,10 @@
         <v>46111.40835648148</v>
       </c>
       <c r="Q635" s="3">
-        <v>46307.41046296297</v>
+        <v>46308.71045138889</v>
       </c>
       <c r="R635">
-        <v>138.9</v>
+        <v>144.9</v>
       </c>
       <c r="S635" t="s">
         <v>4873</v>
@@ -64829,19 +64829,19 @@
         <v>2405</v>
       </c>
       <c r="M653">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N653" t="s">
-        <v>4803</v>
+        <v>4841</v>
       </c>
       <c r="O653" t="s">
-        <v>4871</v>
+        <v>4870</v>
       </c>
       <c r="P653" s="3">
         <v>46273.43547453704</v>
       </c>
       <c r="Q653" s="3">
-        <v>46273.43547453704</v>
+        <v>46308.70836805556</v>
       </c>
       <c r="R653">
         <v>11.9</v>
@@ -77135,7 +77135,7 @@
         <v>4764</v>
       </c>
       <c r="M815">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N815" t="s">
         <v>4804</v>
@@ -77147,7 +77147,7 @@
         <v>46237.50297453703</v>
       </c>
       <c r="Q815" s="3">
-        <v>46248.80214120371</v>
+        <v>46308.70835648148</v>
       </c>
       <c r="R815">
         <v>21.5</v>

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee, Green Burner, Other, Turmeric Curcumin</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -732,7 +732,7 @@
         <v>46088.58265046297</v>
       </c>
       <c r="Q3" s="1" t="n">
-        <v>46309.54239583333</v>
+        <v>46314.3959837963</v>
       </c>
       <c r="R3" t="n">
         <v>66.3</v>
@@ -2206,11 +2206,11 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Spearmint</t>
+          <t>Ashwagandha Coffee, Green Burner, Other, Spearmint</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2222,7 +2222,7 @@
         <v>46223.65637731482</v>
       </c>
       <c r="Q17" s="1" t="n">
-        <v>46244.42299768519</v>
+        <v>46314.39667824074</v>
       </c>
       <c r="R17" t="n">
         <v>22.8</v>
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>46247.53755787037</v>
       </c>
       <c r="Q18" s="1" t="n">
-        <v>46307.54658564815</v>
+        <v>46314.35015046296</v>
       </c>
       <c r="R18" t="n">
         <v>35.3</v>
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>46166.70627314815</v>
       </c>
       <c r="Q40" s="1" t="n">
-        <v>46310.34240740741</v>
+        <v>46314.35015046296</v>
       </c>
       <c r="R40" t="n">
         <v>35.6</v>
@@ -6540,12 +6540,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>£5K-£10K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6555,7 +6555,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6575,17 +6575,17 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Health, Beauty &amp; Personal Care, Home Supplies</t>
+          <t>Health, Beauty &amp; Personal Care, Food &amp; Beverages</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>96.35</t>
+          <t>95.58</t>
         </is>
       </c>
       <c r="M58" t="n">
@@ -13348,12 +13348,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>8616</t>
+          <t>8696</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -13383,17 +13383,17 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Kitchenware, Food &amp; Beverages, Beauty &amp; Personal Care</t>
+          <t>Kitchenware, Health, Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="M122" t="n">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>4785.0</t>
+          <t>4785</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>171</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -15426,7 +15426,7 @@
         </is>
       </c>
       <c r="M141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>46219.85042824074</v>
       </c>
       <c r="Q141" s="1" t="n">
-        <v>46303.30629629629</v>
+        <v>46314.39209490741</v>
       </c>
       <c r="R141" t="n">
         <v>28</v>
@@ -18271,7 +18271,7 @@
         </is>
       </c>
       <c r="M168" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N168" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>46132.27988425926</v>
       </c>
       <c r="Q168" s="1" t="n">
-        <v>46304.50976851852</v>
+        <v>46314.35015046296</v>
       </c>
       <c r="R168" t="n">
         <v>21.5</v>
@@ -18378,11 +18378,11 @@
         </is>
       </c>
       <c r="M169" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee, Green Burner, Other, Turmeric Curcumin</t>
         </is>
       </c>
       <c r="O169" t="inlineStr">
@@ -18394,7 +18394,7 @@
         <v>46154.55766203703</v>
       </c>
       <c r="Q169" s="1" t="n">
-        <v>46204.67089120371</v>
+        <v>46314.12428240741</v>
       </c>
       <c r="R169" t="n">
         <v>22.3</v>
@@ -18913,7 +18913,7 @@
         </is>
       </c>
       <c r="M174" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N174" t="inlineStr">
         <is>
@@ -18929,7 +18929,7 @@
         <v>46190.55417824074</v>
       </c>
       <c r="Q174" s="1" t="n">
-        <v>46280.49377314815</v>
+        <v>46314.35012731481</v>
       </c>
       <c r="R174" t="n">
         <v>26</v>
@@ -21041,11 +21041,11 @@
         </is>
       </c>
       <c r="M194" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Turmeric Curcumin</t>
+          <t>Ashwagandha Coffee, Green Burner, Hibiscus, Turmeric Curcumin</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
@@ -21057,10 +21057,10 @@
         <v>46128.48199074074</v>
       </c>
       <c r="Q194" s="1" t="n">
-        <v>46313.72791666666</v>
+        <v>46314.39740740741</v>
       </c>
       <c r="R194" t="n">
-        <v>90.40000000000001</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -21420,12 +21420,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>3363</t>
+          <t>2217</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -21455,17 +21455,17 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>Health, Beauty &amp; Personal Care, Books, Magazines &amp; Audio</t>
+          <t>Health, Food &amp; Beverages, Womenswear &amp; Underwear</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>95.74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M198" t="n">
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="M276" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N276" t="inlineStr">
         <is>
@@ -29747,10 +29747,10 @@
         <v>46118.51459490741</v>
       </c>
       <c r="Q276" s="1" t="n">
-        <v>46249.60005787037</v>
+        <v>46314.39944444445</v>
       </c>
       <c r="R276" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -32131,22 +32131,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>971</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>10K-25K</t>
+          <t>5K-10K</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>12227</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -32166,17 +32166,17 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Pet Supplies, Food &amp; Beverages, Health</t>
+          <t>Food &amp; Beverages, Pet Supplies, Textiles &amp; Soft Furnishings</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>97.94</t>
+          <t>100</t>
         </is>
       </c>
       <c r="M299" t="n">
@@ -32666,12 +32666,12 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>£10K-£25K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>23478</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -32681,7 +32681,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
@@ -32701,17 +32701,17 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care, Sports &amp; Outdoor, Home Supplies</t>
+          <t>Sports &amp; Outdoor, Beauty &amp; Personal Care, Fashion Accessories</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>76.24</t>
+          <t>81.23</t>
         </is>
       </c>
       <c r="M304" t="n">
@@ -33201,12 +33201,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£200-£500</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>308</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -33216,7 +33216,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -33236,17 +33236,17 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care, Womenswear &amp; Underwear, Food &amp; Beverages</t>
+          <t>Beauty &amp; Personal Care, Food &amp; Beverages, Kids' Fashion</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>96.05</t>
+          <t>93.18</t>
         </is>
       </c>
       <c r="M309" t="n">
@@ -37029,12 +37029,12 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>£500-£1K</t>
+          <t>£1K-£5K</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -37044,7 +37044,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -37064,17 +37064,17 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Household Appliances, Beauty &amp; Personal Care, Home Supplies</t>
+          <t>Kitchenware, Sports &amp; Outdoor, Home Improvement</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>93.87</t>
+          <t>93.89</t>
         </is>
       </c>
       <c r="M345" t="n">
@@ -40600,7 +40600,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -40610,7 +40610,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>2253.0</t>
+          <t>2253</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -40630,7 +40630,7 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
@@ -42621,7 +42621,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -42631,7 +42631,7 @@
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>1875.0</t>
+          <t>1875</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
@@ -44360,7 +44360,7 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -44370,7 +44370,7 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>9704.0</t>
+          <t>9704</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
@@ -50069,12 +50069,12 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£500-£1K</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>756</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
@@ -50084,7 +50084,7 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -50104,17 +50104,17 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>Health, Home Supplies, Shoes</t>
+          <t>Health, Menswear &amp; Underwear, Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="L469" t="inlineStr">
         <is>
-          <t>95.43</t>
+          <t>95.36</t>
         </is>
       </c>
       <c r="M469" t="n">
@@ -52737,7 +52737,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>1718</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -52747,7 +52747,7 @@
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
@@ -52767,17 +52767,17 @@
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>Health, Food &amp; Beverages, Pet Supplies</t>
+          <t>Health, Pet Supplies, Household Appliances</t>
         </is>
       </c>
       <c r="L494" t="inlineStr">
         <is>
-          <t>96.49</t>
+          <t>96.66</t>
         </is>
       </c>
       <c r="M494" t="n">
@@ -53158,56 +53158,20 @@
           <t>https://www.tiktok.com/@zynislam2</t>
         </is>
       </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>781.0</t>
-        </is>
-      </c>
-      <c r="E498" t="inlineStr">
-        <is>
-          <t>1K-5K</t>
-        </is>
-      </c>
-      <c r="F498" t="inlineStr">
-        <is>
-          <t>1988.0</t>
-        </is>
-      </c>
-      <c r="G498" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="H498" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
+      <c r="C498" t="inlineStr"/>
+      <c r="D498" t="inlineStr"/>
+      <c r="E498" t="inlineStr"/>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr"/>
+      <c r="H498" t="inlineStr"/>
       <c r="I498" t="inlineStr">
         <is>
           <t>South Asian</t>
         </is>
       </c>
-      <c r="J498" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="K498" t="inlineStr">
-        <is>
-          <t>Kitchenware, Beauty &amp; Personal Care, Home Improvement</t>
-        </is>
-      </c>
-      <c r="L498" t="inlineStr">
-        <is>
-          <t>93.65</t>
-        </is>
-      </c>
+      <c r="J498" t="inlineStr"/>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr"/>
       <c r="M498" t="n">
         <v>2</v>
       </c>
@@ -54298,7 +54262,7 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
@@ -54308,7 +54272,7 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>2979</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
@@ -54328,17 +54292,17 @@
       </c>
       <c r="J509" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="K509" t="inlineStr">
         <is>
-          <t>Kitchenware, Household Appliances, Fashion Accessories</t>
+          <t>Kitchenware, Furniture, Food &amp; Beverages</t>
         </is>
       </c>
       <c r="L509" t="inlineStr">
         <is>
-          <t>94.17</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="M509" t="n">
@@ -57001,11 +56965,11 @@
         </is>
       </c>
       <c r="M534" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N534" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Hibiscus</t>
+          <t>Ashwagandha Coffee, Green Burner, Hibiscus, Other</t>
         </is>
       </c>
       <c r="O534" t="inlineStr">
@@ -57017,7 +56981,7 @@
         <v>46084.401875</v>
       </c>
       <c r="Q534" s="1" t="n">
-        <v>46310.57226851852</v>
+        <v>46314.35015046296</v>
       </c>
       <c r="R534" t="n">
         <v>27.3</v>
@@ -58027,7 +57991,7 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -58037,7 +58001,7 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>2480.0</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
@@ -58067,7 +58031,7 @@
       </c>
       <c r="L544" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M544" t="n">
@@ -59410,7 +59374,7 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -59420,7 +59384,7 @@
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>1397.0</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
@@ -62687,7 +62651,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>608</t>
+          <t>508</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -62697,7 +62661,7 @@
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
@@ -62717,17 +62681,17 @@
       </c>
       <c r="J588" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="K588" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care, Womenswear &amp; Underwear, Household Appliances</t>
+          <t>Fashion Accessories, Food &amp; Beverages, Baby &amp; Maternity</t>
         </is>
       </c>
       <c r="L588" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="M588" t="n">
@@ -62901,7 +62865,7 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>349</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
@@ -62911,7 +62875,7 @@
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
@@ -62931,17 +62895,17 @@
       </c>
       <c r="J590" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K590" t="inlineStr">
         <is>
-          <t>Textiles &amp; Soft Furnishings, Home Supplies, Womenswear &amp; Underwear</t>
+          <t>Textiles &amp; Soft Furnishings, Womenswear &amp; Underwear, Beauty &amp; Personal Care</t>
         </is>
       </c>
       <c r="L590" t="inlineStr">
         <is>
-          <t>89.65</t>
+          <t>89.94</t>
         </is>
       </c>
       <c r="M590" t="n">
@@ -66999,7 +66963,7 @@
         </is>
       </c>
       <c r="M628" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N628" t="inlineStr">
         <is>
@@ -67015,7 +66979,7 @@
         <v>46247.90908564815</v>
       </c>
       <c r="Q628" s="1" t="n">
-        <v>46283.4083912037</v>
+        <v>46314.35015046296</v>
       </c>
       <c r="R628" t="n">
         <v>18.4</v>
@@ -67708,11 +67672,11 @@
       <c r="K635" t="inlineStr"/>
       <c r="L635" t="inlineStr"/>
       <c r="M635" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N635" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Hibiscus, Other</t>
+          <t>Ashwagandha, Ashwagandha Coffee, Green Burner, Hibiscus, Other</t>
         </is>
       </c>
       <c r="O635" t="inlineStr">
@@ -67724,10 +67688,10 @@
         <v>46273.43547453704</v>
       </c>
       <c r="Q635" s="1" t="n">
-        <v>46311.39528935185</v>
+        <v>46314.39807870371</v>
       </c>
       <c r="R635" t="n">
-        <v>16.6</v>
+        <v>22.3</v>
       </c>
       <c r="S635" t="inlineStr">
         <is>
@@ -71369,7 +71333,7 @@
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>250.0</t>
+          <t>250</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
@@ -71379,7 +71343,7 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>1736.0</t>
+          <t>1736</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -71409,7 +71373,7 @@
       </c>
       <c r="L670" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="M670" t="n">
@@ -72368,11 +72332,11 @@
         </is>
       </c>
       <c r="M679" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N679" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner</t>
+          <t>Ashwagandha Coffee, Green Burner, Other</t>
         </is>
       </c>
       <c r="O679" t="inlineStr">
@@ -72384,7 +72348,7 @@
         <v>46251.29798611111</v>
       </c>
       <c r="Q679" s="1" t="n">
-        <v>46259.87857638889</v>
+        <v>46314.35013888889</v>
       </c>
       <c r="R679" t="n">
         <v>11.9</v>
@@ -73060,12 +73024,12 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>£1K-£5K</t>
+          <t>£0-£50</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>2423</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
@@ -73075,7 +73039,7 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>74232</t>
+          <t>73966</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -73095,12 +73059,12 @@
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K686" t="inlineStr">
         <is>
-          <t>Beauty &amp; Personal Care, Womenswear &amp; Underwear, Health</t>
+          <t>Health, Tools &amp; Hardware, Food &amp; Beverages</t>
         </is>
       </c>
       <c r="L686" t="inlineStr">
@@ -76466,52 +76430,16 @@
           <t>https://www.tiktok.com/@lauu2tiktokshop</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr">
-        <is>
-          <t>£0-£50</t>
-        </is>
-      </c>
-      <c r="D718" t="inlineStr">
-        <is>
-          <t>37.0</t>
-        </is>
-      </c>
-      <c r="E718" t="inlineStr">
-        <is>
-          <t>5K-10K</t>
-        </is>
-      </c>
-      <c r="F718" t="inlineStr">
-        <is>
-          <t>9024.0</t>
-        </is>
-      </c>
-      <c r="G718" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="H718" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
+      <c r="C718" t="inlineStr"/>
+      <c r="D718" t="inlineStr"/>
+      <c r="E718" t="inlineStr"/>
+      <c r="F718" t="inlineStr"/>
+      <c r="G718" t="inlineStr"/>
+      <c r="H718" t="inlineStr"/>
       <c r="I718" t="inlineStr"/>
-      <c r="J718" t="inlineStr">
-        <is>
-          <t>2.87</t>
-        </is>
-      </c>
-      <c r="K718" t="inlineStr">
-        <is>
-          <t>Womenswear &amp; Underwear, Sports &amp; Outdoor, Household Appliances</t>
-        </is>
-      </c>
-      <c r="L718" t="inlineStr">
-        <is>
-          <t>97.8</t>
-        </is>
-      </c>
+      <c r="J718" t="inlineStr"/>
+      <c r="K718" t="inlineStr"/>
+      <c r="L718" t="inlineStr"/>
       <c r="M718" t="n">
         <v>2</v>
       </c>
@@ -83946,11 +83874,11 @@
         </is>
       </c>
       <c r="M789" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N789" t="inlineStr">
         <is>
-          <t>Ashwagandha Coffee, Green Burner, Hibiscus</t>
+          <t>Ashwagandha Coffee, Green Burner, Hibiscus, Other</t>
         </is>
       </c>
       <c r="O789" t="inlineStr">
@@ -83962,7 +83890,7 @@
         <v>46113.58751157407</v>
       </c>
       <c r="Q789" s="1" t="n">
-        <v>46310.5215625</v>
+        <v>46314.35013888889</v>
       </c>
       <c r="R789" t="n">
         <v>100.2</v>
@@ -84116,7 +84044,7 @@
       </c>
       <c r="D791" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="E791" t="inlineStr">
@@ -84126,7 +84054,7 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>139160</t>
+          <t>137280</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
@@ -84146,17 +84074,17 @@
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="K791" t="inlineStr">
         <is>
-          <t>Health, Beauty &amp; Personal Care, Home Supplies</t>
+          <t>Health, Beauty &amp; Personal Care, Home Improvement</t>
         </is>
       </c>
       <c r="L791" t="inlineStr">
         <is>
-          <t>97.24</t>
+          <t>97.35</t>
         </is>
       </c>
       <c r="M791" t="n">
@@ -85333,7 +85261,7 @@
         </is>
       </c>
       <c r="M802" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N802" t="inlineStr">
         <is>
@@ -85349,7 +85277,7 @@
         <v>46220.44594907408</v>
       </c>
       <c r="Q802" s="1" t="n">
-        <v>46265.50358796296</v>
+        <v>46314.39806712963</v>
       </c>
       <c r="R802" t="n">
         <v>16.9</v>
@@ -85817,51 +85745,19 @@
           <t>https://www.tiktok.com/@wearing.it.well</t>
         </is>
       </c>
-      <c r="C807" t="inlineStr">
-        <is>
-          <t>£500-£1K</t>
-        </is>
-      </c>
-      <c r="D807" t="inlineStr">
-        <is>
-          <t>542.0</t>
-        </is>
-      </c>
-      <c r="E807" t="inlineStr">
-        <is>
-          <t>0-1K</t>
-        </is>
-      </c>
-      <c r="F807" t="inlineStr">
-        <is>
-          <t>768.0</t>
-        </is>
-      </c>
-      <c r="G807" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="H807" t="inlineStr">
-        <is>
-          <t>35-44</t>
-        </is>
-      </c>
+      <c r="C807" t="inlineStr"/>
+      <c r="D807" t="inlineStr"/>
+      <c r="E807" t="inlineStr"/>
+      <c r="F807" t="inlineStr"/>
+      <c r="G807" t="inlineStr"/>
+      <c r="H807" t="inlineStr"/>
       <c r="I807" t="inlineStr">
         <is>
           <t>White/European</t>
         </is>
       </c>
-      <c r="J807" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="K807" t="inlineStr">
-        <is>
-          <t>Health, Beauty &amp; Personal Care, Toys &amp; Hobbies</t>
-        </is>
-      </c>
+      <c r="J807" t="inlineStr"/>
+      <c r="K807" t="inlineStr"/>
       <c r="L807" t="inlineStr"/>
       <c r="M807" t="n">
         <v>3</v>
@@ -90179,7 +90075,7 @@
       </c>
       <c r="D848" t="inlineStr">
         <is>
-          <t>3319</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="E848" t="inlineStr">
@@ -90189,7 +90085,7 @@
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="G848" t="inlineStr">
@@ -90209,17 +90105,17 @@
       </c>
       <c r="J848" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="K848" t="inlineStr">
         <is>
-          <t>Household Appliances, Baby &amp; Maternity, Beauty &amp; Personal Care</t>
+          <t>Beauty &amp; Personal Care, Food &amp; Beverages, Health</t>
         </is>
       </c>
       <c r="L848" t="inlineStr">
         <is>
-          <t>95.81</t>
+          <t>94.91</t>
         </is>
       </c>
       <c r="M848" t="n">

--- a/top_creators.xlsx
+++ b/top_creators.xlsx
@@ -14780,13 +14780,13 @@
         <v>4750</v>
       </c>
       <c r="T2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="U2">
         <v>24337.23</v>
       </c>
       <c r="V2">
-        <v>1020</v>
+        <v>933</v>
       </c>
       <c r="W2">
         <v>313523</v>
@@ -14857,13 +14857,13 @@
         <v>4750</v>
       </c>
       <c r="T3">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U3">
         <v>19765.76</v>
       </c>
       <c r="V3">
-        <v>754</v>
+        <v>682</v>
       </c>
       <c r="W3">
         <v>442433</v>
@@ -14940,7 +14940,7 @@
         <v>17454.48</v>
       </c>
       <c r="V4">
-        <v>478</v>
+        <v>419</v>
       </c>
       <c r="W4">
         <v>232903</v>
@@ -15011,13 +15011,13 @@
         <v>4750</v>
       </c>
       <c r="T5">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="U5">
         <v>15908.38</v>
       </c>
       <c r="V5">
-        <v>637</v>
+        <v>582</v>
       </c>
       <c r="W5">
         <v>486728</v>
@@ -15094,7 +15094,7 @@
         <v>14270.14</v>
       </c>
       <c r="V6">
-        <v>365</v>
+        <v>324</v>
       </c>
       <c r="W6">
         <v>292536</v>
@@ -15171,7 +15171,7 @@
         <v>12409.53</v>
       </c>
       <c r="V7">
-        <v>448</v>
+        <v>394</v>
       </c>
       <c r="W7">
         <v>627171</v>
@@ -15245,7 +15245,7 @@
         <v>10114.67</v>
       </c>
       <c r="V8">
-        <v>466</v>
+        <v>432</v>
       </c>
       <c r="W8">
         <v>844359</v>
@@ -15322,7 +15322,7 @@
         <v>8038.43</v>
       </c>
       <c r="V9">
-        <v>342</v>
+        <v>308</v>
       </c>
       <c r="W9">
         <v>270052</v>
@@ -15399,7 +15399,7 @@
         <v>7766.16</v>
       </c>
       <c r="V10">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="W10">
         <v>977408</v>
@@ -15473,7 +15473,7 @@
         <v>6937.08</v>
       </c>
       <c r="V11">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="W11">
         <v>601921</v>
@@ -15550,7 +15550,7 @@
         <v>6772.22</v>
       </c>
       <c r="V12">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="W12">
         <v>121689</v>
@@ -15621,13 +15621,13 @@
         <v>4750</v>
       </c>
       <c r="T13">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="U13">
         <v>6672.84</v>
       </c>
       <c r="V13">
-        <v>261</v>
+        <v>218</v>
       </c>
       <c r="W13">
         <v>375127</v>
@@ -15704,7 +15704,7 @@
         <v>5447.86</v>
       </c>
       <c r="V14">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="W14">
         <v>530035</v>
@@ -15781,7 +15781,7 @@
         <v>5214.47</v>
       </c>
       <c r="V15">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="W15">
         <v>319</v>
@@ -15858,7 +15858,7 @@
         <v>4922.34</v>
       </c>
       <c r="V16">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="W16">
         <v>241015</v>
@@ -15929,13 +15929,13 @@
         <v>4750</v>
       </c>
       <c r="T17">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="U17">
         <v>4569.37</v>
       </c>
       <c r="V17">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="W17">
         <v>184789</v>
@@ -16012,7 +16012,7 @@
         <v>4494.14</v>
       </c>
       <c r="V18">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="W18">
         <v>68335</v>
@@ -16089,7 +16089,7 @@
         <v>4026.85</v>
       </c>
       <c r="V19">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="W19">
         <v>132516</v>
@@ -16166,7 +16166,7 @@
         <v>3864.07</v>
       </c>
       <c r="V20">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="W20">
         <v>262699</v>
@@ -16243,7 +16243,7 @@
         <v>3416.76</v>
       </c>
       <c r="V21">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="W21">
         <v>111112</v>
@@ -16320,7 +16320,7 @@
         <v>3228.3</v>
       </c>
       <c r="V22">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="W22">
         <v>265416</v>
@@ -16397,7 +16397,7 @@
         <v>3103.52</v>
       </c>
       <c r="V23">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="W23">
         <v>133746</v>
@@ -16474,7 +16474,7 @@
         <v>3088.01</v>
       </c>
       <c r="V24">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="W24">
         <v>138744</v>
@@ -16551,7 +16551,7 @@
         <v>3007.49</v>
       </c>
       <c r="V25">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="W25">
         <v>123384</v>
@@ -16628,7 +16628,7 @@
         <v>2806.01</v>
       </c>
       <c r="V26">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="W26">
         <v>110221</v>
@@ -16705,7 +16705,7 @@
         <v>2788.92</v>
       </c>
       <c r="V27">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="W27">
         <v>104492</v>
@@ -16782,7 +16782,7 @@
         <v>2421.59</v>
       </c>
       <c r="V28">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="W28">
         <v>244572</v>
@@ -16859,7 +16859,7 @@
         <v>2249.74</v>
       </c>
       <c r="V29">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="W29">
         <v>135256</v>
@@ -16936,7 +16936,7 @@
         <v>2160.37</v>
       </c>
       <c r="V30">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="W30">
         <v>103920</v>
@@ -17013,7 +17013,7 @@
         <v>1978.2</v>
       </c>
       <c r="V31">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="W31">
         <v>42844</v>
@@ -17090,7 +17090,7 @@
         <v>1962.17</v>
       </c>
       <c r="V32">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="W32">
         <v>131</v>
@@ -17167,7 +17167,7 @@
         <v>1951.48</v>
       </c>
       <c r="V33">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="W33">
         <v>16152</v>
@@ -17244,7 +17244,7 @@
         <v>1926.22</v>
       </c>
       <c r="V34">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="W34">
         <v>135927</v>
@@ -17321,7 +17321,7 @@
         <v>1870.55</v>
       </c>
       <c r="V35">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="W35">
         <v>32077</v>
@@ -17398,7 +17398,7 @@
         <v>1862.45</v>
       </c>
       <c r="V36">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="W36">
         <v>299142</v>
@@ -17475,7 +17475,7 @@
         <v>1857.94</v>
       </c>
       <c r="V37">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="W37">
         <v>31358</v>
@@ -17552,7 +17552,7 @@
         <v>1684.16</v>
       </c>
       <c r="V38">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="W38">
         <v>61428</v>
@@ -17629,7 +17629,7 @@
         <v>1615.26</v>
       </c>
       <c r="V39">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="W39">
         <v>139593</v>
@@ -17706,7 +17706,7 @@
         <v>1514.32</v>
       </c>
       <c r="V40">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="W40">
         <v>93543</v>
@@ -17783,7 +17783,7 @@
         <v>1446.39</v>
       </c>
       <c r="V41">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="W41">
         <v>75039</v>
@@ -17860,7 +17860,7 @@
         <v>1345.07</v>
       </c>
       <c r="V42">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="W42">
         <v>58372</v>
@@ -18014,7 +18014,7 @@
         <v>1277.17</v>
       </c>
       <c r="V44">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="W44">
         <v>13413</v>
@@ -18091,7 +18091,7 @@
         <v>1235.42</v>
       </c>
       <c r="V45">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="W45">
         <v>109574</v>
@@ -18168,7 +18168,7 @@
         <v>1166.99</v>
       </c>
       <c r="V46">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="W46">
         <v>31519</v>
@@ -18245,7 +18245,7 @@
         <v>1145.27</v>
       </c>
       <c r="V47">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="W47">
         <v>10367</v>
@@ -18322,7 +18322,7 @@
         <v>1137.48</v>
       </c>
       <c r="V48">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="W48">
         <v>63962</v>
@@ -18399,7 +18399,7 @@
         <v>1125.57</v>
       </c>
       <c r="V49">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="W49">
         <v>23762</v>
@@ -18476,7 +18476,7 @@
         <v>1097.38</v>
       </c>
       <c r="V50">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="W50">
         <v>58732</v>
@@ -18553,7 +18553,7 @@
         <v>1056.01</v>
       </c>
       <c r="V51">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="W51">
         <v>52223</v>
@@ -18627,7 +18627,7 @@
         <v>1021</v>
       </c>
       <c r="V52">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W52">
         <v>19711</v>
@@ -18704,7 +18704,7 @@
         <v>982.04</v>
       </c>
       <c r="V53">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="W53">
         <v>19712</v>
@@ -18781,7 +18781,7 @@
         <v>955.92</v>
       </c>
       <c r="V54">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="W54">
         <v>61494</v>
@@ -18858,7 +18858,7 @@
         <v>939.58</v>
       </c>
       <c r="V55">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="W55">
         <v>43982</v>
@@ -19009,7 +19009,7 @@
         <v>917.15</v>
       </c>
       <c r="V57">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="W57">
         <v>30642</v>
@@ -19086,7 +19086,7 @@
         <v>894.73</v>
       </c>
       <c r="V58">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="W58">
         <v>11304</v>
@@ -19163,7 +19163,7 @@
         <v>890.37</v>
       </c>
       <c r="V59">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="W59">
         <v>43897</v>
@@ -19240,7 +19240,7 @@
         <v>885.38</v>
       </c>
       <c r="V60">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="W60">
         <v>95646</v>
@@ -19317,7 +19317,7 @@
         <v>880.83</v>
       </c>
       <c r="V61">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="W61">
         <v>41751</v>
@@ -19394,7 +19394,7 @@
         <v>876.6900000000001</v>
       </c>
       <c r="V62">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="W62">
         <v>28944</v>
@@ -19471,7 +19471,7 @@
         <v>842.87</v>
       </c>
       <c r="V63">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="W63">
         <v>14579</v>
@@ -19542,13 +19542,13 @@
         <v>4750</v>
       </c>
       <c r="T64">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U64">
         <v>837.6900000000001</v>
       </c>
       <c r="V64">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="W64">
         <v>37460</v>
@@ -19625,7 +19625,7 @@
         <v>781.33</v>
       </c>
       <c r="V65">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="W65">
         <v>80816</v>
@@ -19696,13 +19696,13 @@
         <v>4750</v>
       </c>
       <c r="T66">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U66">
         <v>778.08</v>
       </c>
       <c r="V66">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="W66">
         <v>10245</v>
@@ -19779,7 +19779,7 @@
         <v>772.92</v>
       </c>
       <c r="V67">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="W67">
         <v>42339</v>
@@ -19856,7 +19856,7 @@
         <v>772.42</v>
       </c>
       <c r="V68">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="W68">
         <v>19</v>
@@ -19933,7 +19933,7 @@
         <v>767.53</v>
       </c>
       <c r="V69">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W69">
         <v>48150</v>
@@ -20010,7 +20010,7 @@
         <v>763.47</v>
       </c>
       <c r="V70">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="W70">
         <v>7505</v>
@@ -20087,7 +20087,7 @@
         <v>755.9400000000001</v>
       </c>
       <c r="V71">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W71">
         <v>99807</v>
@@ -20164,7 +20164,7 @@
         <v>745.62</v>
       </c>
       <c r="V72">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="W72">
         <v>10308</v>
@@ -20241,7 +20241,7 @@
         <v>743.36</v>
       </c>
       <c r="V73">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="W73">
         <v>10332</v>
@@ -20318,7 +20318,7 @@
         <v>734.92</v>
       </c>
       <c r="V74">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="W74">
         <v>36345</v>
@@ -20395,7 +20395,7 @@
         <v>720.02</v>
       </c>
       <c r="V75">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="W75">
         <v>20446</v>
@@ -20472,7 +20472,7 @@
         <v>719.13</v>
       </c>
       <c r="V76">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="W76">
         <v>35170</v>
@@ -20549,7 +20549,7 @@
         <v>707.62</v>
       </c>
       <c r="V77">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="W77">
         <v>16002</v>
@@ -20682,7 +20682,7 @@
         <v>685.0599999999999</v>
       </c>
       <c r="V79">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="W79">
         <v>5408</v>
@@ -20759,7 +20759,7 @@
         <v>653.11</v>
       </c>
       <c r="V80">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="W80">
         <v>3761</v>
@@ -20836,7 +20836,7 @@
         <v>642.12</v>
       </c>
       <c r="V81">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W81">
         <v>9836</v>
@@ -20913,7 +20913,7 @@
         <v>640.46</v>
       </c>
       <c r="V82">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="W82">
         <v>10419</v>
@@ -20984,13 +20984,13 @@
         <v>4750</v>
       </c>
       <c r="T83">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U83">
         <v>636.66</v>
       </c>
       <c r="V83">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="W83">
         <v>5049</v>
@@ -21061,13 +21061,13 @@
         <v>4750</v>
       </c>
       <c r="T84">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="U84">
         <v>616.52</v>
       </c>
       <c r="V84">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="W84">
         <v>6542</v>
@@ -21144,7 +21144,7 @@
         <v>599.09</v>
       </c>
       <c r="V85">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W85">
         <v>43521</v>
@@ -21221,7 +21221,7 @@
         <v>584.86</v>
       </c>
       <c r="V86">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W86">
         <v>4</v>
@@ -21298,7 +21298,7 @@
         <v>582.87</v>
       </c>
       <c r="V87">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="W87">
         <v>58793</v>
@@ -21606,7 +21606,7 @@
         <v>556.21</v>
       </c>
       <c r="V91">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W91">
         <v>20351</v>
@@ -21760,7 +21760,7 @@
         <v>534.6900000000001</v>
       </c>
       <c r="V93">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="W93">
         <v>4524</v>
@@ -21837,7 +21837,7 @@
         <v>521.64</v>
       </c>
       <c r="V94">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="W94">
         <v>9030</v>
@@ -21914,7 +21914,7 @@
         <v>514.2</v>
       </c>
       <c r="V95">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="W95">
         <v>21625</v>
@@ -21991,7 +21991,7 @@
         <v>501.95</v>
       </c>
       <c r="V96">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="W96">
         <v>9445</v>
@@ -22068,7 +22068,7 @@
         <v>491.83</v>
       </c>
       <c r="V97">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="W97">
         <v>5151</v>
@@ -22219,7 +22219,7 @@
         <v>478.31</v>
       </c>
       <c r="V99">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="W99">
         <v>0</v>
@@ -22370,7 +22370,7 @@
         <v>472.81</v>
       </c>
       <c r="V101">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="W101">
         <v>14312</v>
@@ -22447,7 +22447,7 @@
         <v>472.55</v>
       </c>
       <c r="V102">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W102">
         <v>11830</v>
@@ -22524,7 +22524,7 @@
         <v>464.13</v>
       </c>
       <c r="V103">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W103">
         <v>29480</v>
@@ -22755,7 +22755,7 @@
         <v>456.11</v>
       </c>
       <c r="V106">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="W106">
         <v>10208</v>
@@ -23063,7 +23063,7 @@
         <v>404.94</v>
       </c>
       <c r="V110">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W110">
         <v>14931</v>
@@ -23294,7 +23294,7 @@
         <v>385.72</v>
       </c>
       <c r="V113">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W113">
         <v>10708</v>
@@ -23371,7 +23371,7 @@
         <v>385.31</v>
       </c>
       <c r="V114">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W114">
         <v>13186</v>
@@ -23525,7 +23525,7 @@
         <v>380.41</v>
       </c>
       <c r="V116">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W116">
         <v>18700</v>
@@ -23602,7 +23602,7 @@
         <v>366.23</v>
       </c>
       <c r="V117">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W117">
         <v>4859</v>
@@ -23679,7 +23679,7 @@
         <v>365.34</v>
       </c>
       <c r="V118">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W118">
         <v>1902</v>
@@ -23756,7 +23756,7 @@
         <v>351.81</v>
       </c>
       <c r="V119">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W119">
         <v>3284</v>
@@ -23833,7 +23833,7 @@
         <v>349.71</v>
       </c>
       <c r="V120">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W120">
         <v>10000</v>
@@ -23910,7 +23910,7 @@
         <v>346.93</v>
       </c>
       <c r="V121">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W121">
         <v>33375</v>
@@ -23984,7 +23984,7 @@
         <v>344.38</v>
       </c>
       <c r="V122">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="W122">
         <v>26956</v>
@@ -24061,7 +24061,7 @@
         <v>344.07</v>
       </c>
       <c r="V123">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W123">
         <v>971</v>
@@ -24138,7 +24138,7 @@
         <v>342.55</v>
       </c>
       <c r="V124">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="W124">
         <v>2</v>
@@ -24292,7 +24292,7 @@
         <v>335.6</v>
       </c>
       <c r="V126">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W126">
         <v>7212</v>
@@ -24446,7 +24446,7 @@
         <v>333.69</v>
       </c>
       <c r="V128">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="W128">
         <v>5513</v>
@@ -24523,7 +24523,7 @@
         <v>331.71</v>
       </c>
       <c r="V129">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W129">
         <v>67907</v>
@@ -24600,7 +24600,7 @@
         <v>321.59</v>
       </c>
       <c r="V130">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="W130">
         <v>25795</v>
@@ -24754,7 +24754,7 @@
         <v>318.76</v>
       </c>
       <c r="V132">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W132">
         <v>10440</v>
@@ -24831,7 +24831,7 @@
         <v>317.4</v>
       </c>
       <c r="V133">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W133">
         <v>36298</v>
@@ -24908,7 +24908,7 @@
         <v>315.03</v>
       </c>
       <c r="V134">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W134">
         <v>32774</v>
@@ -25062,7 +25062,7 @@
         <v>311.66</v>
       </c>
       <c r="V136">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W136">
         <v>37079</v>
@@ -25139,7 +25139,7 @@
         <v>311.04</v>
       </c>
       <c r="V137">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W137">
         <v>2250</v>
@@ -25213,7 +25213,7 @@
         <v>305.39</v>
       </c>
       <c r="V138">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W138">
         <v>6902</v>
@@ -25290,7 +25290,7 @@
         <v>304.71</v>
       </c>
       <c r="V139">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W139">
         <v>13175</v>
@@ -25367,7 +25367,7 @@
         <v>303.49</v>
       </c>
       <c r="V140">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W140">
         <v>15664</v>
@@ -25598,7 +25598,7 @@
         <v>281.97</v>
       </c>
       <c r="V143">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W143">
         <v>599</v>
@@ -25675,7 +25675,7 @@
         <v>280.97</v>
       </c>
       <c r="V144">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W144">
         <v>11028</v>
@@ -25903,7 +25903,7 @@
         <v>275.75</v>
       </c>
       <c r="V147">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W147">
         <v>5503</v>
@@ -25980,7 +25980,7 @@
         <v>274.76</v>
       </c>
       <c r="V148">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="W148">
         <v>1676</v>
@@ -26057,7 +26057,7 @@
         <v>266.8</v>
       </c>
       <c r="V149">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W149">
         <v>6387</v>
@@ -26134,7 +26134,7 @@
         <v>265.91</v>
       </c>
       <c r="V150">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W150">
         <v>34700</v>
@@ -26211,7 +26211,7 @@
         <v>265.19</v>
       </c>
       <c r="V151">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W151">
         <v>3986</v>
@@ -26288,7 +26288,7 @@
         <v>259.53</v>
       </c>
       <c r="V152">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W152">
         <v>8171</v>
@@ -26516,7 +26516,7 @@
         <v>246.92</v>
       </c>
       <c r="V155">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W155">
         <v>396</v>
@@ -26670,7 +26670,7 @@
         <v>240.11</v>
       </c>
       <c r="V157">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W157">
         <v>25611</v>
@@ -26800,7 +26800,7 @@
         <v>234.65</v>
       </c>
       <c r="V159">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W159">
         <v>8563</v>
@@ -27031,7 +27031,7 @@
         <v>228.29</v>
       </c>
       <c r="V162">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W162">
         <v>9416</v>
@@ -27108,7 +27108,7 @@
         <v>227.73</v>
       </c>
       <c r="V163">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W163">
         <v>10901</v>
@@ -27185,7 +27185,7 @@
         <v>227.13</v>
       </c>
       <c r="V164">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W164">
         <v>45934</v>
@@ -27487,13 +27487,13 @@
         <v>4750</v>
       </c>
       <c r="T168">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U168">
         <v>224.76</v>
       </c>
       <c r="V168">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W168">
         <v>3430</v>
@@ -27644,7 +27644,7 @@
         <v>223.38</v>
       </c>
       <c r="V170">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W170">
         <v>1270</v>
@@ -27721,7 +27721,7 @@
         <v>219.81</v>
       </c>
       <c r="V171">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W171">
         <v>3227</v>
@@ -28029,7 +28029,7 @@
         <v>214.48</v>
       </c>
       <c r="V175">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W175">
         <v>4806</v>
@@ -28106,7 +28106,7 @@
         <v>213.93</v>
       </c>
       <c r="V176">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W176">
         <v>22278</v>
@@ -28180,7 +28180,7 @@
         <v>213.28</v>
       </c>
       <c r="V177">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W177">
         <v>0</v>
@@ -28257,7 +28257,7 @@
         <v>213.11</v>
       </c>
       <c r="V178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W178">
         <v>110</v>
@@ -28334,7 +28334,7 @@
         <v>210.02</v>
       </c>
       <c r="V179">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W179">
         <v>83</v>
@@ -28411,7 +28411,7 @@
         <v>204.71</v>
       </c>
       <c r="V180">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W180">
         <v>13835</v>
@@ -28488,7 +28488,7 @@
         <v>204.43</v>
       </c>
       <c r="V181">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W181">
         <v>9357</v>
@@ -28565,7 +28565,7 @@
         <v>203.95</v>
       </c>
       <c r="V182">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W182">
         <v>31373</v>
@@ -28950,7 +28950,7 @@
         <v>190.12</v>
       </c>
       <c r="V187">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W187">
         <v>6180</v>
@@ -29104,7 +29104,7 @@
         <v>187.77</v>
       </c>
       <c r="V189">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W189">
         <v>0</v>
@@ -29332,7 +29332,7 @@
         <v>179.6</v>
       </c>
       <c r="V192">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W192">
         <v>10082</v>
@@ -29409,7 +29409,7 @@
         <v>176.65</v>
       </c>
       <c r="V193">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W193">
         <v>2276</v>
@@ -29791,7 +29791,7 @@
         <v>171.2</v>
       </c>
       <c r="V198">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W198">
         <v>62</v>
@@ -29868,7 +29868,7 @@
         <v>170.92</v>
       </c>
       <c r="V199">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W199">
         <v>38</v>
@@ -29945,7 +29945,7 @@
         <v>169.06</v>
       </c>
       <c r="V200">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W200">
         <v>815</v>
@@ -30022,7 +30022,7 @@
         <v>168.14</v>
       </c>
       <c r="V201">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="W201">
         <v>7808</v>
@@ -30099,7 +30099,7 @@
         <v>168.05</v>
       </c>
       <c r="V202">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W202">
         <v>5475</v>
@@ -30176,7 +30176,7 @@
         <v>164.48</v>
       </c>
       <c r="V203">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W203">
         <v>359</v>
@@ -30253,7 +30253,7 @@
         <v>162.95</v>
       </c>
       <c r="V204">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W204">
         <v>379</v>
@@ -30484,7 +30484,7 @@
         <v>160.31</v>
       </c>
       <c r="V207">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W207">
         <v>3129</v>
@@ -30715,7 +30715,7 @@
         <v>156.01</v>
       </c>
       <c r="V210">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W210">
         <v>17309</v>
@@ -31325,7 +31325,7 @@
         <v>144.52</v>
       </c>
       <c r="V218">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W218">
         <v>12012</v>
@@ -31479,7 +31479,7 @@
         <v>138.97</v>
       </c>
       <c r="V220">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W220">
         <v>10</v>
@@ -31556,7 +31556,7 @@
         <v>138.15</v>
       </c>
       <c r="V221">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W221">
         <v>945</v>
@@ -31787,7 +31787,7 @@
         <v>134.74</v>
       </c>
       <c r="V224">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W224">
         <v>9498</v>
@@ -31935,7 +31935,7 @@
         <v>132.43</v>
       </c>
       <c r="V226">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W226">
         <v>2962</v>
@@ -32394,7 +32394,7 @@
         <v>128.75</v>
       </c>
       <c r="V232">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W232">
         <v>798</v>
@@ -32468,7 +32468,7 @@
         <v>126.8</v>
       </c>
       <c r="V233">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W233">
         <v>5063</v>
@@ -32545,7 +32545,7 @@
         <v>126.29</v>
       </c>
       <c r="V234">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W234">
         <v>1329</v>
@@ -32776,7 +32776,7 @@
         <v>122.9</v>
       </c>
       <c r="V237">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W237">
         <v>1798</v>
@@ -33134,7 +33134,7 @@
         <v>116.11</v>
       </c>
       <c r="V242">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W242">
         <v>3954</v>
@@ -33211,7 +33211,7 @@
         <v>116.09</v>
       </c>
       <c r="V243">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W243">
         <v>204</v>
@@ -33516,7 +33516,7 @@
         <v>114.16</v>
       </c>
       <c r="V247">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W247">
         <v>30</v>
@@ -33590,7 +33590,7 @@
         <v>112.64</v>
       </c>
       <c r="V248">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W248">
         <v>244</v>
@@ -34354,7 +34354,7 @@
         <v>109.49</v>
       </c>
       <c r="V258">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W258">
         <v>0</v>
@@ -34508,7 +34508,7 @@
         <v>108.97</v>
       </c>
       <c r="V260">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W260">
         <v>3023</v>
@@ -34816,7 +34816,7 @@
         <v>105.69</v>
       </c>
       <c r="V264">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W264">
         <v>53</v>
@@ -34967,7 +34967,7 @@
         <v>104.97</v>
       </c>
       <c r="V266">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W266">
         <v>3658</v>
@@ -35044,16 +35044,16 @@
         <v>104.29</v>
       </c>
       <c r="V267">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W267">
         <v>15</v>
       </c>
       <c r="X267" s="3">
-        <v>46276</v>
+        <v>46289</v>
       </c>
       <c r="Y267">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="268" spans="1:25">
@@ -35198,7 +35198,7 @@
         <v>102.88</v>
       </c>
       <c r="V269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W269">
         <v>3682</v>
@@ -35275,7 +35275,7 @@
         <v>102.85</v>
       </c>
       <c r="V270">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="W270">
         <v>1971</v>
@@ -35506,7 +35506,7 @@
         <v>99.23999999999999</v>
       </c>
       <c r="V273">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W273">
         <v>1880</v>
@@ -35583,7 +35583,7 @@
         <v>99.03</v>
       </c>
       <c r="V274">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W274">
         <v>2229</v>
@@ -36116,7 +36116,7 @@
         <v>95.13</v>
       </c>
       <c r="V281">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W281">
         <v>3010</v>
@@ -36424,7 +36424,7 @@
         <v>93.84999999999999</v>
       </c>
       <c r="V285">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W285">
         <v>1613</v>
@@ -36578,7 +36578,7 @@
         <v>92.94</v>
       </c>
       <c r="V287">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W287">
         <v>5484</v>
@@ -37040,7 +37040,7 @@
         <v>90.95999999999999</v>
       </c>
       <c r="V293">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W293">
         <v>1104</v>
@@ -37117,7 +37117,7 @@
         <v>90.05</v>
       </c>
       <c r="V294">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W294">
         <v>1080</v>
@@ -37271,7 +37271,7 @@
         <v>89.83</v>
       </c>
       <c r="V296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W296">
         <v>39</v>
@@ -37348,7 +37348,7 @@
         <v>88.95999999999999</v>
       </c>
       <c r="V297">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W297">
         <v>107</v>
@@ -37425,7 +37425,7 @@
         <v>88.93000000000001</v>
       </c>
       <c r="V298">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W298">
         <v>12</v>
@@ -37656,7 +37656,7 @@
         <v>86.98999999999999</v>
       </c>
       <c r="V301">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W301">
         <v>30</v>
@@ -38041,7 +38041,7 @@
         <v>85.56999999999999</v>
       </c>
       <c r="V306">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W306">
         <v>8959</v>
@@ -38118,7 +38118,7 @@
         <v>85.45999999999999</v>
       </c>
       <c r="V307">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W307">
         <v>2750</v>
@@ -38426,7 +38426,7 @@
         <v>84.73</v>
       </c>
       <c r="V311">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W311">
         <v>11638</v>
@@ -38888,7 +38888,7 @@
         <v>83.17</v>
       </c>
       <c r="V317">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="W317">
         <v>314</v>
@@ -39169,7 +39169,7 @@
         <v>80.87</v>
       </c>
       <c r="V321">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W321">
         <v>0</v>
@@ -39243,7 +39243,7 @@
         <v>80.61</v>
       </c>
       <c r="V322">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W322">
         <v>427</v>
@@ -39394,7 +39394,7 @@
         <v>79.92</v>
       </c>
       <c r="V324">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W324">
         <v>5167</v>
@@ -39471,7 +39471,7 @@
         <v>79.81999999999999</v>
       </c>
       <c r="V325">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W325">
         <v>762</v>
@@ -40155,7 +40155,7 @@
         <v>76.94</v>
       </c>
       <c r="V334">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W334">
         <v>944</v>
@@ -40386,7 +40386,7 @@
         <v>76.25</v>
       </c>
       <c r="V337">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W337">
         <v>3206</v>
@@ -40463,7 +40463,7 @@
         <v>75.43000000000001</v>
       </c>
       <c r="V338">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W338">
         <v>7</v>
@@ -40617,7 +40617,7 @@
         <v>74.5</v>
       </c>
       <c r="V340">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W340">
         <v>1650</v>
@@ -41052,7 +41052,7 @@
         <v>72.95999999999999</v>
       </c>
       <c r="V346">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W346">
         <v>16</v>
@@ -41129,7 +41129,7 @@
         <v>72.59</v>
       </c>
       <c r="V347">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W347">
         <v>28</v>
@@ -41360,7 +41360,7 @@
         <v>72.19</v>
       </c>
       <c r="V350">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W350">
         <v>12576</v>
@@ -41514,7 +41514,7 @@
         <v>69.34999999999999</v>
       </c>
       <c r="V352">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W352">
         <v>216</v>
@@ -41588,7 +41588,7 @@
         <v>69.2</v>
       </c>
       <c r="V353">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W353">
         <v>2</v>
@@ -41665,7 +41665,7 @@
         <v>68.78</v>
       </c>
       <c r="V354">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W354">
         <v>2533</v>
@@ -41896,7 +41896,7 @@
         <v>68.36</v>
       </c>
       <c r="V357">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W357">
         <v>10871</v>
@@ -42180,7 +42180,7 @@
         <v>67.95999999999999</v>
       </c>
       <c r="V361">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W361">
         <v>5206</v>
@@ -42796,7 +42796,7 @@
         <v>65.16</v>
       </c>
       <c r="V369">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W369">
         <v>1393</v>
@@ -43480,7 +43480,7 @@
         <v>61.93</v>
       </c>
       <c r="V378">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W378">
         <v>880</v>
@@ -43634,7 +43634,7 @@
         <v>61.84</v>
       </c>
       <c r="V380">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W380">
         <v>317</v>
@@ -44374,7 +44374,7 @@
         <v>60.03</v>
       </c>
       <c r="V390">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W390">
         <v>2945</v>
@@ -44451,7 +44451,7 @@
         <v>60.02</v>
       </c>
       <c r="V391">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W391">
         <v>848</v>
@@ -44602,7 +44602,7 @@
         <v>60.02</v>
       </c>
       <c r="V393">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W393">
         <v>4</v>
@@ -44753,7 +44753,7 @@
         <v>59.99</v>
       </c>
       <c r="V395">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W395">
         <v>161</v>
@@ -44907,7 +44907,7 @@
         <v>59.99</v>
       </c>
       <c r="V397">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W397">
         <v>342</v>
@@ -44984,7 +44984,7 @@
         <v>59.99</v>
       </c>
       <c r="V398">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W398">
         <v>668</v>
@@ -45570,7 +45570,7 @@
         <v>59.09</v>
       </c>
       <c r="V406">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W406">
         <v>1318</v>
@@ -45647,7 +45647,7 @@
         <v>59.04</v>
       </c>
       <c r="V407">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W407">
         <v>52</v>
@@ -46186,7 +46186,7 @@
         <v>57.81</v>
       </c>
       <c r="V414">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W414">
         <v>79</v>
@@ -46340,7 +46340,7 @@
         <v>57.09</v>
       </c>
       <c r="V416">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W416">
         <v>48</v>
@@ -46417,7 +46417,7 @@
         <v>57.09</v>
       </c>
       <c r="V417">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W417">
         <v>784</v>
@@ -46494,7 +46494,7 @@
         <v>57.02</v>
       </c>
       <c r="V418">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W418">
         <v>0</v>
@@ -46571,7 +46571,7 @@
         <v>56.99</v>
       </c>
       <c r="V419">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W419">
         <v>983</v>
@@ -46799,7 +46799,7 @@
         <v>56.84</v>
       </c>
       <c r="V422">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W422">
         <v>542</v>
@@ -46876,7 +46876,7 @@
         <v>56.8</v>
       </c>
       <c r="V423">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W423">
         <v>0</v>
@@ -46929,7 +46929,7 @@
         <v>55.92</v>
       </c>
       <c r="V424">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W424">
         <v>5410</v>
@@ -47080,7 +47080,7 @@
         <v>55.14</v>
       </c>
       <c r="V426">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W426">
         <v>87</v>
@@ -47157,7 +47157,7 @@
         <v>55.11</v>
       </c>
       <c r="V427">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W427">
         <v>583</v>
@@ -47619,7 +47619,7 @@
         <v>54.89</v>
       </c>
       <c r="V433">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W433">
         <v>640</v>
@@ -47770,7 +47770,7 @@
         <v>54.49</v>
       </c>
       <c r="V435">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W435">
         <v>31580</v>
@@ -48149,7 +48149,7 @@
         <v>53.28</v>
       </c>
       <c r="V440">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="W440">
         <v>649</v>
@@ -48534,7 +48534,7 @@
         <v>51.92</v>
       </c>
       <c r="V445">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W445">
         <v>23</v>
@@ -48993,7 +48993,7 @@
         <v>49.99</v>
       </c>
       <c r="V451">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W451">
         <v>0</v>
@@ -49677,7 +49677,7 @@
         <v>49.01</v>
       </c>
       <c r="V460">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W460">
         <v>1244</v>
@@ -49985,7 +49985,7 @@
         <v>48.66</v>
       </c>
       <c r="V464">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W464">
         <v>693</v>
@@ -50669,7 +50669,7 @@
         <v>46.4</v>
       </c>
       <c r="V473">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W473">
         <v>2519</v>
@@ -50746,7 +50746,7 @@
         <v>45.68</v>
       </c>
       <c r="V474">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W474">
         <v>24</v>
@@ -50900,7 +50900,7 @@
         <v>44.99</v>
       </c>
       <c r="V476">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W476">
         <v>376</v>
@@ -51282,7 +51282,7 @@
         <v>44.91</v>
       </c>
       <c r="V481">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W481">
         <v>282</v>
@@ -54397,7 +54397,7 @@
         <v>40.09</v>
       </c>
       <c r="V522">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W522">
         <v>982</v>
@@ -55700,7 +55700,7 @@
         <v>39.91</v>
       </c>
       <c r="V539">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W539">
         <v>36</v>
@@ -56929,7 +56929,7 @@
         <v>36.13</v>
       </c>
       <c r="V555">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="W555">
         <v>1414</v>
@@ -59005,7 +59005,7 @@
         <v>33.34</v>
       </c>
       <c r="V582">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W582">
         <v>258</v>
@@ -61380,7 +61380,7 @@
         <v>28.62</v>
       </c>
       <c r="V613">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W613">
         <v>42</v>
@@ -61904,13 +61904,13 @@
         <v>4750</v>
       </c>
       <c r="T620">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U620">
         <v>28.26</v>
       </c>
       <c r="V620">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W620">
         <v>48</v>
@@ -62736,13 +62736,13 @@
         <v>4750</v>
       </c>
       <c r="T631">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="U631">
         <v>26.91</v>
       </c>
       <c r="V631">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W631">
         <v>1384</v>
@@ -65105,7 +65105,7 @@
         <v>24.8</v>
       </c>
       <c r="V662">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W662">
         <v>319</v>
@@ -66402,22 +66402,22 @@
         <v>4750</v>
       </c>
       <c r="T679">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U679">
         <v>23.99</v>
       </c>
       <c r="V679">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W679">
         <v>491</v>
       </c>
       <c r="X679" s="3">
-        <v>46257</v>
+        <v>46276</v>
       </c>
       <c r="Y679">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
     <row r="680" spans="1:25">
@@ -68563,7 +68563,7 @@
         <v>19.99</v>
       </c>
       <c r="V708">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W708">
         <v>584</v>
@@ -69649,7 +69649,7 @@
         <v>19.13</v>
       </c>
       <c r="V723">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W723">
         <v>120</v>
@@ -71606,7 +71606,7 @@
         <v>18.99</v>
       </c>
       <c r="V749">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W749">
         <v>458</v>
@@ -71683,7 +71683,7 @@
         <v>18.99</v>
       </c>
       <c r="V750">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W750">
         <v>1300</v>
@@ -73202,22 +73202,22 @@
         <v>4750</v>
       </c>
       <c r="T770">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U770">
         <v>16</v>
       </c>
       <c r="V770">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W770">
         <v>497</v>
       </c>
       <c r="X770" s="3">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="Y770">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="771" spans="1:25">
@@ -75352,7 +75352,7 @@
         <v>14.22</v>
       </c>
       <c r="V798">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W798">
         <v>2922</v>
@@ -77176,22 +77176,22 @@
         <v>4750</v>
       </c>
       <c r="T822">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U822">
         <v>9.99</v>
       </c>
       <c r="V822">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W822">
         <v>1742</v>
       </c>
       <c r="X822" s="3">
-        <v>46257</v>
+        <v>46265</v>
       </c>
       <c r="Y822">
-        <v>142</v>
+        <v>150</v>
       </c>
     </row>
     <row r="823" spans="1:25">
